--- a/r5-core-main/StructureDefinition-at-core-location.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T09:10:20+00:00</t>
+    <t>2026-03-01T19:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-location.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:31:53+00:00</t>
+    <t>2026-07-17T05:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
